--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
@@ -832,7 +832,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
@@ -76,13 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ZAID RAUL</t>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>EDNA YOSSELIN</t>
   </si>
 </sst>
 </file>
@@ -600,16 +600,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -623,16 +626,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -646,16 +652,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -711,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>87.18000000000001</v>
+        <v>84.62</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -746,7 +755,7 @@
         <v>80</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -763,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -814,7 +823,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920268</v>
+        <v>22330051920383</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -829,10 +838,10 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,15 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>EDNA YOSSELIN</t>
   </si>
 </sst>
 </file>
@@ -791,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -821,29 +812,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920383</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
   </si>
 </sst>
 </file>
@@ -746,7 +764,7 @@
         <v>80</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -763,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -782,7 +800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -812,6 +830,52 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920157</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920270</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,19 +76,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>FLORES</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>MARIA DE LOS ANGELES</t>
@@ -729,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -781,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -800,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -832,47 +823,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920157</v>
+        <v>22330051920270</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920270</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>
